--- a/data/trans_dic/IP31KM02_R_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_R_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>68,78%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>60,36; 76,14</t>
+          <t>60,94; 76,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,93; 77,42</t>
+          <t>58,74; 74,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,94; 74,65</t>
+          <t>63,02; 73,51</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>65,23%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,73; 71,68</t>
+          <t>56,63; 74,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55,3; 73,35</t>
+          <t>56,06; 72,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58,2; 69,7</t>
+          <t>58,43; 70,88</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,85%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,39; 78,38</t>
+          <t>56,45; 77,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,92; 75,43</t>
+          <t>51,6; 77,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,28; 73,12</t>
+          <t>57,84; 74,31</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>58,72%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,18; 57,76</t>
+          <t>53,36; 68,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>52,82; 67,63</t>
+          <t>48,91; 61,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,05; 59,95</t>
+          <t>53,68; 63,68</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,82%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>61,56; 76,34</t>
+          <t>64,56; 79,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>65,0; 79,53</t>
+          <t>61,31; 75,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65,84; 76,42</t>
+          <t>65,46; 76,34</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>70,89%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64,09; 81,53</t>
+          <t>57,68; 77,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53,46; 75,22</t>
+          <t>64,66; 81,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62,5; 76,17</t>
+          <t>63,6; 77,2</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>65,82%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>52,43; 65,83</t>
+          <t>63,51; 70,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>62,64; 69,63</t>
+          <t>60,99; 67,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59,59; 66,84</t>
+          <t>63,48; 68,39</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>104</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69662</t>
+          <t>84144</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95003</t>
+          <t>68243</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>164665</t>
+          <t>152386</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>61387; 77440</t>
+          <t>73861; 92893</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85068; 104651</t>
+          <t>58943; 75028</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>151473; 176826</t>
+          <t>139617; 162866</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>87</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>59568</t>
+          <t>59486</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>60821</t>
+          <t>61375</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>120390</t>
+          <t>120861</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51112; 66944</t>
+          <t>50899; 66822</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51820; 68737</t>
+          <t>53485; 68845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>108884; 130406</t>
+          <t>108262; 131330</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>37578</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40281</t>
+          <t>34518</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73974</t>
+          <t>72096</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26743; 39259</t>
+          <t>31521; 43168</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32987; 47016</t>
+          <t>26837; 40446</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63271; 82207</t>
+          <t>62385; 80148</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>153</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>103275</t>
+          <t>121527</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>128643</t>
+          <t>98043</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>231919</t>
+          <t>219570</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71506; 124489</t>
+          <t>105283; 134517</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>112317; 143827</t>
+          <t>86395; 108616</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>184357; 256688</t>
+          <t>200754; 238146</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>117</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>80101</t>
+          <t>104831</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>115181</t>
+          <t>80056</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195282</t>
+          <t>184887</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>71113; 88176</t>
+          <t>93984; 115730</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103655; 126827</t>
+          <t>70792; 87484</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>181049; 210142</t>
+          <t>170896; 199296</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>70</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>50887</t>
+          <t>44495</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>45111</t>
+          <t>52070</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95998</t>
+          <t>96566</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44156; 56172</t>
+          <t>37988; 50910</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36906; 51925</t>
+          <t>45490; 57211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86206; 105059</t>
+          <t>86638; 105158</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>583</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>397186</t>
+          <t>452060</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>485041</t>
+          <t>394305</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>882227</t>
+          <t>846365</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>338272; 424695</t>
+          <t>429111; 474881</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>458721; 509971</t>
+          <t>372167; 414575</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>820914; 920713</t>
+          <t>816263; 879415</t>
         </is>
       </c>
     </row>
